--- a/public/data/CONVERSOR_EXCEL_A_DASHBOARD.xlsx
+++ b/public/data/CONVERSOR_EXCEL_A_DASHBOARD.xlsx
@@ -13,20 +13,26 @@
     <sheet name="DATOS_EPM" sheetId="5" r:id="rId5"/>
     <sheet name="CONTROL" sheetId="6" r:id="rId6"/>
     <sheet name="INCIDENCIAS" sheetId="7" r:id="rId7"/>
+    <sheet name="PROMOCION" sheetId="8" r:id="rId8"/>
+    <sheet name="FILAS" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="ALUMNADO" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="cASIG">CATALOGO!$A$2:$A$201</definedName>
     <definedName name="cESP">CATALOGO!$C$2:$C$201</definedName>
     <definedName name="cETAPA">CATALOGO!$B$2:$B$201</definedName>
+    <definedName name="eANO">INDEX(eBLOQUE,0,_xlfn.XMATCH("anoacademico_id",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eAPRUEBA">INDEX(eBLOQUE,0,_xlfn.XMATCH("aprueba",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eASIG">INDEX(eBLOQUE,0,_xlfn.XMATCH("co_desc",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eBLOQUE">ENTRADA!$A$2:INDEX(ENTRADA!$AZ:$AZ,MAX(2,CONTROL!$B$4))</definedName>
+    <definedName name="eCENTRO">INDEX(eBLOQUE,0,_xlfn.XMATCH("denominacionespecifica",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eCODIGO">INDEX(eBLOQUE,0,_xlfn.XMATCH("co_codigo",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eCURSO">INDEX(eBLOQUE,0,_xlfn.XMATCH("curso_cont",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eCURSOMAT">INDEX(eBLOQUE,0,_xlfn.XMATCH("curso_mat",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eEVAL">INDEX(eBLOQUE,0,_xlfn.XMATCH("ev_codigo",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eNIA">INDEX(eBLOQUE,0,_xlfn.XMATCH("nia",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eNOTA">INDEX(eBLOQUE,0,_xlfn.XMATCH("nota",ENTRADA!$A$1:$AZ$1))</definedName>
+    <definedName name="ePROMOCIONA">INDEX(eBLOQUE,0,_xlfn.XMATCH("promociona",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eTIPO">INDEX(eBLOQUE,0,_xlfn.XMATCH("co_tipobasico",ENTRADA!$A$1:$AZ$1))</definedName>
     <definedName name="eULTIMA">CONTROL!$B$4</definedName>
   </definedNames>
@@ -133,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -148,6 +154,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -271,82 +280,163 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">QUÉ HACE CON LOS DATOS</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 · PROMOCION: qué pasa con cada alumno</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Etapa: la del curso de la asignatura (…EEM o …EPM).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Curso: el de la asignatura, también en las pendientes. La Armonía de 4.º que cursa un alumno de 5.º cuenta en 4.º, con el resto de la Armonía de 4.º.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">Promoción y titulación por curso, alumnado por número de suspensas, pendientes y recuperación en la extraordinaria. Se calcula aquí mismo, sin pasar por los analizadores, y son solo recuentos: ningún NIA ni ningún nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Filas sin nota: se descartan. Son sobre todo la extraordinaria de quien aprobó en la ordinaria; si pasaran, borrarían su nota de junio y contarían como un cero.</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUÉ HACE CON LOS DATOS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIA: se sustituye por un número. Es el mismo para el mismo alumno dentro de este fichero, y basta para que el analizador cruce ordinaria y extraordinaria. Nombre, apellidos y sexo no pasan.</t>
+          <t xml:space="preserve">Etapa: la del curso de la asignatura (…EEM o …EPM).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Especialidad: la exportación no la trae; es la asignatura del alumno que CATALOGO marca como especialidad. Quien tiene dos conserva sus comunes repetidas, y el analizador lo avisa.</t>
+          <t xml:space="preserve">Curso: el de la asignatura, también en las pendientes. La Armonía de 4.º que cursa un alumno de 5.º cuenta en 4.º, con el resto de la Armonía de 4.º.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asignatura: con el nombre del catálogo. La que no esté pasa con el suyo, y el analizador la cuenta en «FueraDeLasCifras».</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+          <t xml:space="preserve">Filas sin nota: se descartan. Son sobre todo la extraordinaria de quien aprobó en la ordinaria; si pasaran, borrarían su nota de junio y contarían como un cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NIA: se sustituye por un número. Es el mismo para el mismo alumno dentro de este fichero, y basta para que el analizador cruce ordinaria y extraordinaria. Nombre, apellidos y sexo no pasan.</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANTES DE GUARDAR O COMPARTIR</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Especialidad: la exportación no la trae; es la asignatura del alumno que CATALOGO marca como especialidad. Quien tiene dos conserva sus comunes repetidas, y el analizador lo avisa.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Asignatura: con el nombre del catálogo. La que no esté pasa con el suyo, y el analizador la cuenta en «FueraDeLasCifras».</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANTES DE GUARDAR O COMPARTIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ENTRADA contiene datos personales. Cuando hayas copiado las dos hojas, borra ENTRADA: el conversor vacío no guarda nada de nadie, y los analizadores solo reciben números.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CATALOGO tiene que decir lo mismo que los analizadores. Si añades una asignatura a uno de ellos, añádela aquí también, con su etapa.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">José Luis Miralles Bono · www.jlmirall.es · Desarrollado con Claude (Anthropic)</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alumno</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etapa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notas</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suspensas finales</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decisión</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" cm="1">
+        <f t="array" ref="A2">IF(CONTROL!$B$4&lt;2,"",_xlfn.LET(_xlpm.vF,_xlfn.ANCHORARRAY(FILAS!$A$2),_xlpm.vIdF,INDEX(_xlpm.vF,0,1),_xlpm.vCur,INDEX(_xlpm.vF,0,2),_xlpm.vEval,INDEX(_xlpm.vF,0,5),_xlpm.vFin,INDEX(_xlpm.vF,0,10),_xlpm.vPr,INDEX(_xlpm.vF,0,11),_xlpm.vU,_xlfn.UNIQUE(_xlpm.vIdF),_xlpm.vM,--(_xlpm.vU=TRANSPOSE(_xlpm.vIdF)),_xlpm.vConNota,(_xlpm.vEval&lt;&gt;"EX")*ISNUMBER(_xlpm.vFin),_xlpm.vSusp,_xlpm.vConNota*(IF(ISNUMBER(_xlpm.vFin),_xlpm.vFin,99)&lt;5),_xlpm.vNotas,MMULT(_xlpm.vM,_xlpm.vConNota),_xlpm.vNSusp,MMULT(_xlpm.vM,_xlpm.vSusp),_xlpm.vCurso,_xlfn.XLOOKUP(_xlpm.vU,_xlpm.vIdF,_xlpm.vCur),_xlpm.vPEx,_xlfn.XLOOKUP(_xlpm.vU,_xlfn._xlws.FILTER(_xlpm.vIdF,(_xlpm.vEval="EX")*(_xlpm.vPr&lt;&gt;""),-1),_xlfn._xlws.FILTER(_xlpm.vPr,(_xlpm.vEval="EX")*(_xlpm.vPr&lt;&gt;""),""),""),_xlpm.vPOtra,_xlfn.XLOOKUP(_xlpm.vU,_xlfn._xlws.FILTER(_xlpm.vIdF,(_xlpm.vEval&lt;&gt;"EX")*(_xlpm.vPr&lt;&gt;""),-1),_xlfn._xlws.FILTER(_xlpm.vPr,(_xlpm.vEval&lt;&gt;"EX")*(_xlpm.vPr&lt;&gt;""),""),""),_xlpm.vDec,IF(_xlpm.vPEx&lt;&gt;"",_xlpm.vPEx,_xlpm.vPOtra),_xlpm.vEstado,IF(_xlpm.vDec="1","Promociona",IF(_xlpm.vDec="0","No promociona","Sin decisión")),_xlpm.vEvalA,IF((_xlpm.vNotas&gt;0)+(_xlpm.vDec&lt;&gt;"")&gt;0,"Con evaluación","Sin evaluación"),CHOOSE({1,2,3,4,5,6,7,8},_xlpm.vU,_xlpm.vCurso,RIGHT(_xlpm.vCurso,3),_xlpm.vNotas,_xlpm.vNSusp,_xlpm.vDec,_xlpm.vEstado,_xlpm.vEvalA)))</f>
       </c>
     </row>
   </sheetData>
@@ -2274,6 +2364,21 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Columnas opcionales que faltan</t>
+        </is>
+      </c>
+      <c r="B22" s="3" cm="1">
+        <f t="array" ref="B22">_xlfn.LET(_xlpm.vC,{"promociona","anoacademico_id","denominacionespecifica"},_xlpm.vL,_xlfn.TEXTJOIN(", ",TRUE,IF(ISNA(_xlfn.XMATCH(_xlpm.vC,ENTRADA!$A$1:$AZ$1)),_xlpm.vC,"")),IF(_xlpm.vL="","Ninguna",_xlpm.vL))</f>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin «promociona», PROMOCION no puede dar decisiones de promoción; el resto de sus recuentos, sí.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2439,4 +2544,1555 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF047857"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promoción, titulación y resultados del alumnado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" cm="1">
+        <f t="array" ref="A2">IF(CONTROL!$B$4&lt;2,"Pega la exportación en ENTRADA",IFERROR("Año académico "&amp;INDEX(eANO,1),"")&amp;IFERROR(" · "&amp;INDEX(eCENTRO,1),""))</f>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo recuentos: ningún NIA, ningún nombre. Un curso que no aparece en la exportación sale como «—», no como 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Promoción por curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un alumno, una vez, en su curso de matrícula. Manda la decisión de la evaluación más tardía que la trae: la extraordinaria antes que la ordinaria. «Con evaluación»: al menos una nota o una decisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matriculados</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Con evaluación</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promocionan</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No promocionan</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin decisión</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin evaluación</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% promociona sobre evaluados</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% promociona sobre matriculados</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EEM</t>
+        </is>
+      </c>
+      <c r="B8" s="0" cm="1">
+        <f t="array" ref="B8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C8" s="0" cm="1">
+        <f t="array" ref="C8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D8" s="0" cm="1">
+        <f t="array" ref="D8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E8" s="0" cm="1">
+        <f t="array" ref="E8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F8" s="0" cm="1">
+        <f t="array" ref="F8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G8" s="0" cm="1">
+        <f t="array" ref="G8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H8" s="7" cm="1">
+        <f t="array" ref="H8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I8" s="7" cm="1">
+        <f t="array" ref="I8">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2EEM</t>
+        </is>
+      </c>
+      <c r="B9" s="0" cm="1">
+        <f t="array" ref="B9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C9" s="0" cm="1">
+        <f t="array" ref="C9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D9" s="0" cm="1">
+        <f t="array" ref="D9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E9" s="0" cm="1">
+        <f t="array" ref="E9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F9" s="0" cm="1">
+        <f t="array" ref="F9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G9" s="0" cm="1">
+        <f t="array" ref="G9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H9" s="7" cm="1">
+        <f t="array" ref="H9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I9" s="7" cm="1">
+        <f t="array" ref="I9">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EEM</t>
+        </is>
+      </c>
+      <c r="B10" s="0" cm="1">
+        <f t="array" ref="B10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C10" s="0" cm="1">
+        <f t="array" ref="C10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D10" s="0" cm="1">
+        <f t="array" ref="D10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E10" s="0" cm="1">
+        <f t="array" ref="E10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F10" s="0" cm="1">
+        <f t="array" ref="F10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G10" s="0" cm="1">
+        <f t="array" ref="G10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H10" s="7" cm="1">
+        <f t="array" ref="H10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I10" s="7" cm="1">
+        <f t="array" ref="I10">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EEM</t>
+        </is>
+      </c>
+      <c r="B11" s="0" cm="1">
+        <f t="array" ref="B11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C11" s="0" cm="1">
+        <f t="array" ref="C11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D11" s="0" cm="1">
+        <f t="array" ref="D11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E11" s="0" cm="1">
+        <f t="array" ref="E11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F11" s="0" cm="1">
+        <f t="array" ref="F11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G11" s="0" cm="1">
+        <f t="array" ref="G11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H11" s="7" cm="1">
+        <f t="array" ref="H11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I11" s="7" cm="1">
+        <f t="array" ref="I11">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total EEM</t>
+        </is>
+      </c>
+      <c r="B12" s="0" cm="1">
+        <f t="array" ref="B12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C12" s="0" cm="1">
+        <f t="array" ref="C12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D12" s="0" cm="1">
+        <f t="array" ref="D12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E12" s="0" cm="1">
+        <f t="array" ref="E12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F12" s="0" cm="1">
+        <f t="array" ref="F12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G12" s="0" cm="1">
+        <f t="array" ref="G12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H12" s="7" cm="1">
+        <f t="array" ref="H12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I12" s="7" cm="1">
+        <f t="array" ref="I12">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EPM</t>
+        </is>
+      </c>
+      <c r="B13" s="0" cm="1">
+        <f t="array" ref="B13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C13" s="0" cm="1">
+        <f t="array" ref="C13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D13" s="0" cm="1">
+        <f t="array" ref="D13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E13" s="0" cm="1">
+        <f t="array" ref="E13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F13" s="0" cm="1">
+        <f t="array" ref="F13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G13" s="0" cm="1">
+        <f t="array" ref="G13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H13" s="7" cm="1">
+        <f t="array" ref="H13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I13" s="7" cm="1">
+        <f t="array" ref="I13">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2EPM</t>
+        </is>
+      </c>
+      <c r="B14" s="0" cm="1">
+        <f t="array" ref="B14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C14" s="0" cm="1">
+        <f t="array" ref="C14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D14" s="0" cm="1">
+        <f t="array" ref="D14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E14" s="0" cm="1">
+        <f t="array" ref="E14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F14" s="0" cm="1">
+        <f t="array" ref="F14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G14" s="0" cm="1">
+        <f t="array" ref="G14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H14" s="7" cm="1">
+        <f t="array" ref="H14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I14" s="7" cm="1">
+        <f t="array" ref="I14">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EPM</t>
+        </is>
+      </c>
+      <c r="B15" s="0" cm="1">
+        <f t="array" ref="B15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C15" s="0" cm="1">
+        <f t="array" ref="C15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D15" s="0" cm="1">
+        <f t="array" ref="D15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E15" s="0" cm="1">
+        <f t="array" ref="E15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F15" s="0" cm="1">
+        <f t="array" ref="F15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G15" s="0" cm="1">
+        <f t="array" ref="G15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H15" s="7" cm="1">
+        <f t="array" ref="H15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I15" s="7" cm="1">
+        <f t="array" ref="I15">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EPM</t>
+        </is>
+      </c>
+      <c r="B16" s="0" cm="1">
+        <f t="array" ref="B16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C16" s="0" cm="1">
+        <f t="array" ref="C16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D16" s="0" cm="1">
+        <f t="array" ref="D16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E16" s="0" cm="1">
+        <f t="array" ref="E16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F16" s="0" cm="1">
+        <f t="array" ref="F16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G16" s="0" cm="1">
+        <f t="array" ref="G16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H16" s="7" cm="1">
+        <f t="array" ref="H16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I16" s="7" cm="1">
+        <f t="array" ref="I16">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5EPM</t>
+        </is>
+      </c>
+      <c r="B17" s="0" cm="1">
+        <f t="array" ref="B17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C17" s="0" cm="1">
+        <f t="array" ref="C17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D17" s="0" cm="1">
+        <f t="array" ref="D17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E17" s="0" cm="1">
+        <f t="array" ref="E17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F17" s="0" cm="1">
+        <f t="array" ref="F17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G17" s="0" cm="1">
+        <f t="array" ref="G17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H17" s="7" cm="1">
+        <f t="array" ref="H17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I17" s="7" cm="1">
+        <f t="array" ref="I17">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6EPM</t>
+        </is>
+      </c>
+      <c r="B18" s="0" cm="1">
+        <f t="array" ref="B18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C18" s="0" cm="1">
+        <f t="array" ref="C18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D18" s="0" cm="1">
+        <f t="array" ref="D18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E18" s="0" cm="1">
+        <f t="array" ref="E18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F18" s="0" cm="1">
+        <f t="array" ref="F18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G18" s="0" cm="1">
+        <f t="array" ref="G18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H18" s="7" cm="1">
+        <f t="array" ref="H18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I18" s="7" cm="1">
+        <f t="array" ref="I18">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total EPM</t>
+        </is>
+      </c>
+      <c r="B19" s="0" cm="1">
+        <f t="array" ref="B19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C19" s="0" cm="1">
+        <f t="array" ref="C19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D19" s="0" cm="1">
+        <f t="array" ref="D19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E19" s="0" cm="1">
+        <f t="array" ref="E19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F19" s="0" cm="1">
+        <f t="array" ref="F19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G19" s="0" cm="1">
+        <f t="array" ref="G19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H19" s="7" cm="1">
+        <f t="array" ref="H19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I19" s="7" cm="1">
+        <f t="array" ref="I19">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total</t>
+        </is>
+      </c>
+      <c r="B20" s="0" cm="1">
+        <f t="array" ref="B20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C20" s="0" cm="1">
+        <f t="array" ref="C20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D20" s="0" cm="1">
+        <f t="array" ref="D20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E20" s="0" cm="1">
+        <f t="array" ref="E20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="No promociona"))))),"—"))</f>
+      </c>
+      <c r="F20" s="0" cm="1">
+        <f t="array" ref="F20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Sin decisión")))),"—"))</f>
+      </c>
+      <c r="G20" s="0" cm="1">
+        <f t="array" ref="G20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Sin evaluación")))),"—"))</f>
+      </c>
+      <c r="H20" s="7" cm="1">
+        <f t="array" ref="H20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+      <c r="I20" s="7" cm="1">
+        <f t="array" ref="I20">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/_xlpm.vN))),"—"))</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Finalizan elementales y titulan en profesionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finalizar es promocionar en 4EEM y titular, en 6EPM, según la columna promociona. Al lado, quién termina sin ninguna suspensa: si la exportación no rellena la decisión, es la otra lectura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matriculados</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Con evaluación</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finalizan o titulan, según la exportación</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminan sin ninguna suspensa</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% sobre evaluados</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EEM</t>
+        </is>
+      </c>
+      <c r="B25" s="0" cm="1">
+        <f t="array" ref="B25">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C25" s="0" cm="1">
+        <f t="array" ref="C25">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D25" s="0" cm="1">
+        <f t="array" ref="D25">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E25" s="0" cm="1">
+        <f t="array" ref="E25">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="F25" s="7" cm="1">
+        <f t="array" ref="F25">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6EPM</t>
+        </is>
+      </c>
+      <c r="B26" s="0" cm="1">
+        <f t="array" ref="B26">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",_xlpm.vN)),"—"))</f>
+      </c>
+      <c r="C26" s="0" cm="1">
+        <f t="array" ref="C26">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")))),"—"))</f>
+      </c>
+      <c r="D26" s="0" cm="1">
+        <f t="array" ref="D26">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))))),"—"))</f>
+      </c>
+      <c r="E26" s="0" cm="1">
+        <f t="array" ref="E26">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="F26" s="7" cm="1">
+        <f t="array" ref="F26">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IF(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,6)&lt;&gt;""))=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,7)="Promociona"))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,8)="Con evaluación")),"—")))),"—"))</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Alumnado por número de asignaturas suspensas</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Con la nota final de cada asignatura: la de la extraordinaria si la hay. Es un recuento: no aplica ninguna norma de promoción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Con notas</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ninguna</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Una</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dos</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tres o más</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EEM</t>
+        </is>
+      </c>
+      <c r="B31" s="0" cm="1">
+        <f t="array" ref="B31">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C31" s="0" cm="1">
+        <f t="array" ref="C31">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D31" s="0" cm="1">
+        <f t="array" ref="D31">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E31" s="0" cm="1">
+        <f t="array" ref="E31">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F31" s="0" cm="1">
+        <f t="array" ref="F31">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2EEM</t>
+        </is>
+      </c>
+      <c r="B32" s="0" cm="1">
+        <f t="array" ref="B32">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C32" s="0" cm="1">
+        <f t="array" ref="C32">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D32" s="0" cm="1">
+        <f t="array" ref="D32">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E32" s="0" cm="1">
+        <f t="array" ref="E32">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F32" s="0" cm="1">
+        <f t="array" ref="F32">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EEM</t>
+        </is>
+      </c>
+      <c r="B33" s="0" cm="1">
+        <f t="array" ref="B33">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C33" s="0" cm="1">
+        <f t="array" ref="C33">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D33" s="0" cm="1">
+        <f t="array" ref="D33">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E33" s="0" cm="1">
+        <f t="array" ref="E33">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F33" s="0" cm="1">
+        <f t="array" ref="F33">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EEM</t>
+        </is>
+      </c>
+      <c r="B34" s="0" cm="1">
+        <f t="array" ref="B34">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C34" s="0" cm="1">
+        <f t="array" ref="C34">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D34" s="0" cm="1">
+        <f t="array" ref="D34">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E34" s="0" cm="1">
+        <f t="array" ref="E34">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F34" s="0" cm="1">
+        <f t="array" ref="F34">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total EEM</t>
+        </is>
+      </c>
+      <c r="B35" s="0" cm="1">
+        <f t="array" ref="B35">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C35" s="0" cm="1">
+        <f t="array" ref="C35">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D35" s="0" cm="1">
+        <f t="array" ref="D35">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E35" s="0" cm="1">
+        <f t="array" ref="E35">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F35" s="0" cm="1">
+        <f t="array" ref="F35">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EPM</t>
+        </is>
+      </c>
+      <c r="B36" s="0" cm="1">
+        <f t="array" ref="B36">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C36" s="0" cm="1">
+        <f t="array" ref="C36">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D36" s="0" cm="1">
+        <f t="array" ref="D36">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E36" s="0" cm="1">
+        <f t="array" ref="E36">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F36" s="0" cm="1">
+        <f t="array" ref="F36">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2EPM</t>
+        </is>
+      </c>
+      <c r="B37" s="0" cm="1">
+        <f t="array" ref="B37">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C37" s="0" cm="1">
+        <f t="array" ref="C37">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D37" s="0" cm="1">
+        <f t="array" ref="D37">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E37" s="0" cm="1">
+        <f t="array" ref="E37">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F37" s="0" cm="1">
+        <f t="array" ref="F37">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EPM</t>
+        </is>
+      </c>
+      <c r="B38" s="0" cm="1">
+        <f t="array" ref="B38">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C38" s="0" cm="1">
+        <f t="array" ref="C38">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D38" s="0" cm="1">
+        <f t="array" ref="D38">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E38" s="0" cm="1">
+        <f t="array" ref="E38">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F38" s="0" cm="1">
+        <f t="array" ref="F38">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EPM</t>
+        </is>
+      </c>
+      <c r="B39" s="0" cm="1">
+        <f t="array" ref="B39">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C39" s="0" cm="1">
+        <f t="array" ref="C39">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D39" s="0" cm="1">
+        <f t="array" ref="D39">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E39" s="0" cm="1">
+        <f t="array" ref="E39">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F39" s="0" cm="1">
+        <f t="array" ref="F39">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5EPM</t>
+        </is>
+      </c>
+      <c r="B40" s="0" cm="1">
+        <f t="array" ref="B40">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C40" s="0" cm="1">
+        <f t="array" ref="C40">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D40" s="0" cm="1">
+        <f t="array" ref="D40">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E40" s="0" cm="1">
+        <f t="array" ref="E40">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F40" s="0" cm="1">
+        <f t="array" ref="F40">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6EPM</t>
+        </is>
+      </c>
+      <c r="B41" s="0" cm="1">
+        <f t="array" ref="B41">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C41" s="0" cm="1">
+        <f t="array" ref="C41">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D41" s="0" cm="1">
+        <f t="array" ref="D41">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E41" s="0" cm="1">
+        <f t="array" ref="E41">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F41" s="0" cm="1">
+        <f t="array" ref="F41">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total EPM</t>
+        </is>
+      </c>
+      <c r="B42" s="0" cm="1">
+        <f t="array" ref="B42">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C42" s="0" cm="1">
+        <f t="array" ref="C42">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D42" s="0" cm="1">
+        <f t="array" ref="D42">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E42" s="0" cm="1">
+        <f t="array" ref="E42">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F42" s="0" cm="1">
+        <f t="array" ref="F42">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total</t>
+        </is>
+      </c>
+      <c r="B43" s="0" cm="1">
+        <f t="array" ref="B43">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)))),"—"))</f>
+      </c>
+      <c r="C43" s="0" cm="1">
+        <f t="array" ref="C43">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=0)))),"—"))</f>
+      </c>
+      <c r="D43" s="0" cm="1">
+        <f t="array" ref="D43">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=1)))),"—"))</f>
+      </c>
+      <c r="E43" s="0" cm="1">
+        <f t="array" ref="E43">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)=2)))),"—"))</f>
+      </c>
+      <c r="F43" s="0" cm="1">
+        <f t="array" ref="F43">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EEM")+(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,4)&gt;0)*(INDEX(_xlfn.ANCHORARRAY(ALUMNADO!$A$2),0,5)&gt;=3)))),"—"))</f>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Asignaturas pendientes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por curso de matrícula: las pendientes de cursos anteriores que el alumnado cursa este año. Superada: nota final de 5 o más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendientes</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superadas</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No superadas</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EEM</t>
+        </is>
+      </c>
+      <c r="B48" s="0" cm="1">
+        <f t="array" ref="B48">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C48" s="0" cm="1">
+        <f t="array" ref="C48">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D48" s="0" cm="1">
+        <f t="array" ref="D48">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E48" s="0" cm="1">
+        <f t="array" ref="E48">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2EEM</t>
+        </is>
+      </c>
+      <c r="B49" s="0" cm="1">
+        <f t="array" ref="B49">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C49" s="0" cm="1">
+        <f t="array" ref="C49">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D49" s="0" cm="1">
+        <f t="array" ref="D49">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E49" s="0" cm="1">
+        <f t="array" ref="E49">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EEM</t>
+        </is>
+      </c>
+      <c r="B50" s="0" cm="1">
+        <f t="array" ref="B50">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C50" s="0" cm="1">
+        <f t="array" ref="C50">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D50" s="0" cm="1">
+        <f t="array" ref="D50">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E50" s="0" cm="1">
+        <f t="array" ref="E50">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EEM</t>
+        </is>
+      </c>
+      <c r="B51" s="0" cm="1">
+        <f t="array" ref="B51">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C51" s="0" cm="1">
+        <f t="array" ref="C51">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D51" s="0" cm="1">
+        <f t="array" ref="D51">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E51" s="0" cm="1">
+        <f t="array" ref="E51">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total EEM</t>
+        </is>
+      </c>
+      <c r="B52" s="0" cm="1">
+        <f t="array" ref="B52">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C52" s="0" cm="1">
+        <f t="array" ref="C52">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D52" s="0" cm="1">
+        <f t="array" ref="D52">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E52" s="0" cm="1">
+        <f t="array" ref="E52">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EPM</t>
+        </is>
+      </c>
+      <c r="B53" s="0" cm="1">
+        <f t="array" ref="B53">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C53" s="0" cm="1">
+        <f t="array" ref="C53">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D53" s="0" cm="1">
+        <f t="array" ref="D53">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E53" s="0" cm="1">
+        <f t="array" ref="E53">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2EPM</t>
+        </is>
+      </c>
+      <c r="B54" s="0" cm="1">
+        <f t="array" ref="B54">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C54" s="0" cm="1">
+        <f t="array" ref="C54">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D54" s="0" cm="1">
+        <f t="array" ref="D54">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E54" s="0" cm="1">
+        <f t="array" ref="E54">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EPM</t>
+        </is>
+      </c>
+      <c r="B55" s="0" cm="1">
+        <f t="array" ref="B55">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C55" s="0" cm="1">
+        <f t="array" ref="C55">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D55" s="0" cm="1">
+        <f t="array" ref="D55">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E55" s="0" cm="1">
+        <f t="array" ref="E55">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EPM</t>
+        </is>
+      </c>
+      <c r="B56" s="0" cm="1">
+        <f t="array" ref="B56">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C56" s="0" cm="1">
+        <f t="array" ref="C56">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D56" s="0" cm="1">
+        <f t="array" ref="D56">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E56" s="0" cm="1">
+        <f t="array" ref="E56">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5EPM</t>
+        </is>
+      </c>
+      <c r="B57" s="0" cm="1">
+        <f t="array" ref="B57">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C57" s="0" cm="1">
+        <f t="array" ref="C57">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D57" s="0" cm="1">
+        <f t="array" ref="D57">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E57" s="0" cm="1">
+        <f t="array" ref="E57">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6EPM</t>
+        </is>
+      </c>
+      <c r="B58" s="0" cm="1">
+        <f t="array" ref="B58">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C58" s="0" cm="1">
+        <f t="array" ref="C58">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D58" s="0" cm="1">
+        <f t="array" ref="D58">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E58" s="0" cm="1">
+        <f t="array" ref="E58">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total EPM</t>
+        </is>
+      </c>
+      <c r="B59" s="0" cm="1">
+        <f t="array" ref="B59">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C59" s="0" cm="1">
+        <f t="array" ref="C59">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D59" s="0" cm="1">
+        <f t="array" ref="D59">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E59" s="0" cm="1">
+        <f t="array" ref="E59">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total</t>
+        </is>
+      </c>
+      <c r="B60" s="0" cm="1">
+        <f t="array" ref="B60">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM")+(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")))),"—"))</f>
+      </c>
+      <c r="C60" s="0" cm="1">
+        <f t="array" ref="C60">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM")+(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D60" s="0" cm="1">
+        <f t="array" ref="D60">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM")+(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E60" s="0" cm="1">
+        <f t="array" ref="E60">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,((RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EEM")+(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,2),3)="EPM")),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,7)="Pendiente")*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)&lt;&gt;"EX")*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,10)))))),"—"))</f>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. Recuperación en la extraordinaria, por curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo profesional: elemental no tiene extraordinaria. Por curso de la asignatura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suspensas en ordinaria</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperadas en la extraordinaria</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siguen suspensas</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin nota en la extraordinaria</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% recuperado</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EPM</t>
+        </is>
+      </c>
+      <c r="B65" s="0" cm="1">
+        <f t="array" ref="B65">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="C65" s="0" cm="1">
+        <f t="array" ref="C65">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D65" s="0" cm="1">
+        <f t="array" ref="D65">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E65" s="0" cm="1">
+        <f t="array" ref="E65">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)))))),"—"))</f>
+      </c>
+      <c r="F65" s="7" cm="1">
+        <f t="array" ref="F65">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="1EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)),"—"))),"—"))</f>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2EPM</t>
+        </is>
+      </c>
+      <c r="B66" s="0" cm="1">
+        <f t="array" ref="B66">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="C66" s="0" cm="1">
+        <f t="array" ref="C66">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D66" s="0" cm="1">
+        <f t="array" ref="D66">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E66" s="0" cm="1">
+        <f t="array" ref="E66">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)))))),"—"))</f>
+      </c>
+      <c r="F66" s="7" cm="1">
+        <f t="array" ref="F66">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="2EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)),"—"))),"—"))</f>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EPM</t>
+        </is>
+      </c>
+      <c r="B67" s="0" cm="1">
+        <f t="array" ref="B67">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="C67" s="0" cm="1">
+        <f t="array" ref="C67">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D67" s="0" cm="1">
+        <f t="array" ref="D67">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E67" s="0" cm="1">
+        <f t="array" ref="E67">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)))))),"—"))</f>
+      </c>
+      <c r="F67" s="7" cm="1">
+        <f t="array" ref="F67">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="3EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)),"—"))),"—"))</f>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4EPM</t>
+        </is>
+      </c>
+      <c r="B68" s="0" cm="1">
+        <f t="array" ref="B68">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="C68" s="0" cm="1">
+        <f t="array" ref="C68">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D68" s="0" cm="1">
+        <f t="array" ref="D68">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E68" s="0" cm="1">
+        <f t="array" ref="E68">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)))))),"—"))</f>
+      </c>
+      <c r="F68" s="7" cm="1">
+        <f t="array" ref="F68">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="4EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)),"—"))),"—"))</f>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5EPM</t>
+        </is>
+      </c>
+      <c r="B69" s="0" cm="1">
+        <f t="array" ref="B69">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="C69" s="0" cm="1">
+        <f t="array" ref="C69">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D69" s="0" cm="1">
+        <f t="array" ref="D69">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E69" s="0" cm="1">
+        <f t="array" ref="E69">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)))))),"—"))</f>
+      </c>
+      <c r="F69" s="7" cm="1">
+        <f t="array" ref="F69">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="5EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)),"—"))),"—"))</f>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6EPM</t>
+        </is>
+      </c>
+      <c r="B70" s="0" cm="1">
+        <f t="array" ref="B70">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="C70" s="0" cm="1">
+        <f t="array" ref="C70">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D70" s="0" cm="1">
+        <f t="array" ref="D70">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E70" s="0" cm="1">
+        <f t="array" ref="E70">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)))))),"—"))</f>
+      </c>
+      <c r="F70" s="7" cm="1">
+        <f t="array" ref="F70">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3)="6EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)),"—"))),"—"))</f>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total EPM</t>
+        </is>
+      </c>
+      <c r="B71" s="0" cm="1">
+        <f t="array" ref="B71">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="C71" s="0" cm="1">
+        <f t="array" ref="C71">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5)))),"—"))</f>
+      </c>
+      <c r="D71" s="0" cm="1">
+        <f t="array" ref="D71">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),99)&lt;5)))),"—"))</f>
+      </c>
+      <c r="E71" s="0" cm="1">
+        <f t="array" ref="E71">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*(1-ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)))))),"—"))</f>
+      </c>
+      <c r="F71" s="7" cm="1">
+        <f t="array" ref="F71">IF(CONTROL!$B$4&lt;2,"—",IFERROR(_xlfn.LET(_xlpm.vC,(RIGHT(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,3),3)="EPM"),_xlpm.vN,SUM(--(_xlpm.vC)),IF(_xlpm.vN=0,"—",IFERROR(SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,9),0)&gt;=5))/SUM(_xlpm.vC*(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,5)="OR")*ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8))*(IF(ISNUMBER(INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8)),INDEX(_xlfn.ANCHORARRAY(FILAS!$A$2),0,8),99)&lt;5)),"—"))),"—"))</f>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Recuperación en la extraordinaria, por asignatura</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De más a menos suspensas en ordinaria. Solo las asignaturas con alguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignatura</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suspensas en ordinaria</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recuperadas en la extraordinaria</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siguen suspensas</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin nota en la extraordinaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" cm="1">
+        <f t="array" ref="A76">IF(CONTROL!$B$4&lt;2,"Sin datos",IFERROR(_xlfn.LET(_xlpm.vF,_xlfn.ANCHORARRAY(FILAS!$A$2),_xlpm.vN8,INDEX(_xlpm.vF,0,8),_xlpm.vN9,INDEX(_xlpm.vF,0,9),_xlpm.vAs,INDEX(_xlpm.vF,0,6),_xlpm.vCu,INDEX(_xlpm.vF,0,3),_xlpm.vS,(INDEX(_xlpm.vF,0,5)="OR")*ISNUMBER(_xlpm.vN8)*(IF(ISNUMBER(_xlpm.vN8),_xlpm.vN8,99)&lt;5),_xlpm.vU,_xlfn.UNIQUE(_xlfn._xlws.FILTER(CHOOSE({1,2},_xlpm.vAs,_xlpm.vCu),_xlpm.vS)),_xlpm.vM,--((INDEX(_xlpm.vU,0,1)&amp;"|"&amp;INDEX(_xlpm.vU,0,2))=TRANSPOSE(_xlpm.vAs&amp;"|"&amp;_xlpm.vCu)),_xlpm.vRec,_xlpm.vS*ISNUMBER(_xlpm.vN9)*(IF(ISNUMBER(_xlpm.vN9),_xlpm.vN9,0)&gt;=5),_xlpm.vSig,_xlpm.vS*ISNUMBER(_xlpm.vN9)*(IF(ISNUMBER(_xlpm.vN9),_xlpm.vN9,99)&lt;5),_xlpm.vSin,_xlpm.vS*(1-ISNUMBER(_xlpm.vN9)),_xlfn._xlws.SORT(CHOOSE({1,2,3,4,5,6},INDEX(_xlpm.vU,0,1),INDEX(_xlpm.vU,0,2),MMULT(_xlpm.vM,_xlpm.vS),MMULT(_xlpm.vM,_xlpm.vRec),MMULT(_xlpm.vM,_xlpm.vSig),MMULT(_xlpm.vM,_xlpm.vSin)),3,-1)),"Ninguna"))</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alumno</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso matrícula</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso asignatura</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etapa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluación</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignatura</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota en la extraordinaria</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota final</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Promociona</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" cm="1">
+        <f t="array" ref="A2">IF(CONTROL!$B$4&lt;2,"",_xlfn.LET(_xlpm.vEt,RIGHT(eCURSO,3),_xlpm.vAsig,TRIM(eASIG),_xlpm.vCanon,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.vAsig&amp;"|"&amp;_xlpm.vEt,cASIG&amp;"|"&amp;cETAPA,cASIG),_xlpm.vAsig),_xlpm.vEsEsp,ISNUMBER(_xlfn.XMATCH(_xlpm.vAsig&amp;"|"&amp;_xlpm.vEt&amp;"|Sí",cASIG&amp;"|"&amp;cETAPA&amp;"|"&amp;cESP)),_xlpm.vClave,eNIA&amp;"|"&amp;_xlpm.vEt,_xlpm.vTexto,TRIM(eNOTA&amp;""),_xlpm.vNum,IF(_xlpm.vTexto="","",IFERROR(IF(ISNUMBER(SEARCH(",",_xlpm.vTexto)),_xlfn.NUMBERVALUE(_xlpm.vTexto,","),_xlfn.NUMBERVALUE(_xlpm.vTexto,".")),"?")),_xlpm.vId,_xlfn.XMATCH(eNIA&amp;"",_xlfn.UNIQUE(eNIA&amp;"")),_xlpm.vEsEx,TRIM(eEVAL&amp;"")="EX",_xlpm.vKey,_xlpm.vId&amp;"|"&amp;TRIM(eCURSO&amp;"")&amp;"|"&amp;_xlpm.vCanon,_xlpm.vExK,_xlfn._xlws.FILTER(_xlpm.vKey,_xlpm.vEsEx*ISNUMBER(_xlpm.vNum),"~"),_xlpm.vExN,_xlfn._xlws.FILTER(_xlpm.vNum,_xlpm.vEsEx*ISNUMBER(_xlpm.vNum),""),_xlpm.vNotaEx,IF(_xlpm.vEsEx,"",_xlfn.XLOOKUP(_xlpm.vKey,_xlpm.vExK,_xlpm.vExN,"")),_xlpm.vFinal,IF(_xlpm.vEsEx,"",IF(ISNUMBER(_xlpm.vNotaEx),_xlpm.vNotaEx,IF(ISNUMBER(_xlpm.vNum),_xlpm.vNum,""))),_xlpm.vP,UPPER(TRIM(IFERROR(ePROMOCIONA&amp;"",""))),_xlpm.vProm,IF(ISNUMBER(_xlfn.XMATCH(_xlpm.vP,{"1","S","SI","SÍ","TRUE","VERDADERO"})),"1",IF(ISNUMBER(_xlfn.XMATCH(_xlpm.vP,{"0","N","NO","FALSE","FALSO"})),"0","")),CHOOSE({1,2,3,4,5,6,7,8,9,10,11},_xlpm.vId,TRIM(eCURSOMAT&amp;""),TRIM(eCURSO&amp;""),_xlpm.vEt,TRIM(eEVAL&amp;""),_xlpm.vCanon,TRIM(IFERROR(eTIPO&amp;"","")),_xlpm.vNum,_xlpm.vNotaEx,_xlpm.vFinal,_xlpm.vProm)))</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>